--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno4/anno4_task1_empathetic_engagement.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno4/anno4_task1_empathetic_engagement.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26CCBDC-31E8-4040-A0FA-52B16FF1105E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59C495A6-F338-4C8A-BA19-F18626D6C5CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="160">
   <si>
     <t>UID</t>
   </si>
@@ -56,46 +70,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000021-0001</t>
-  </si>
-  <si>
-    <t>Have you heard about the possibility of black holes existing at the beginning of the universe?</t>
-  </si>
-  <si>
-    <t>I haven't heard that one before, that's really interesting!</t>
-  </si>
-  <si>
-    <t>No, I haven't heard that before. That's really interesting!</t>
-  </si>
-  <si>
-    <t>No, I haven't! That's fascinating.</t>
-  </si>
-  <si>
-    <t>No, I haven't heard of that before! That's fascinating.</t>
-  </si>
-  <si>
-    <t>Wow, I had no idea! That's a really interesting concept.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000052-0001</t>
-  </si>
-  <si>
-    <t>I wish I had learned to play an instrument when I was younger.</t>
-  </si>
-  <si>
-    <t>I know the feeling.</t>
-  </si>
-  <si>
-    <t>It's never too late to start learning.</t>
-  </si>
-  <si>
-    <t>It's never too late to start learning now.</t>
-  </si>
-  <si>
-    <t>It's never too late to start!</t>
-  </si>
-  <si>
-    <t>I know what you mean, it's never too late to start though!</t>
+    <t>SFTANNO-000013-0001</t>
+  </si>
+  <si>
+    <t>I've never really thought about it, but I'm interested in exploring more.</t>
+  </si>
+  <si>
+    <t>That's great, there's so much to discover and appreciate!</t>
+  </si>
+  <si>
+    <t>That's great! There are so many different stories and themes within ballet, you're sure to find something you like.</t>
+  </si>
+  <si>
+    <t>That's great! There are so many unique and interesting ballets out there, you'll definitely find something that resonates with you.</t>
+  </si>
+  <si>
+    <t>That's great, I'm sure you'll find something you love!</t>
+  </si>
+  <si>
+    <t>That's great to hear, I think you'll find a lot of interesting stories and themes in ballet.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000182-0001</t>
+  </si>
+  <si>
+    <t>The Holocaust, because I want to understand how such devastation could happen.</t>
+  </si>
+  <si>
+    <t>It's important to learn about history to prevent such tragedies from happening again.</t>
+  </si>
+  <si>
+    <t>It's important to study history to prevent it from repeating itself.</t>
+  </si>
+  <si>
+    <t>It's important to remember and learn from history, especially the sad and difficult parts.</t>
+  </si>
+  <si>
+    <t>It's important to learn about the past to prevent such events from happening again.</t>
+  </si>
+  <si>
+    <t>I'm sorry to hear that.</t>
   </si>
   <si>
     <t>SFTANNO-000019-0001</t>
@@ -161,43 +175,43 @@
     <t>That's so sad to hear. It's like they don't care about the most vulnerable.</t>
   </si>
   <si>
-    <t>SFTANNO-000049-0001</t>
-  </si>
-  <si>
-    <t>The director just announced a new initiative, and I'm genuinely surprised.</t>
-  </si>
-  <si>
-    <t>It's surprising when they introduce something unexpected.</t>
-  </si>
-  <si>
-    <t>I'm surprised too, what's the initiative about?</t>
-  </si>
-  <si>
-    <t>That's unexpected, what's the initiative about?</t>
-  </si>
-  <si>
-    <t>That's unexpected! What's the new initiative about?</t>
-  </si>
-  <si>
-    <t>That's unexpected! What's the initiative about?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000008-0001</t>
-  </si>
-  <si>
-    <t>I've been thinking about volunteering at an animal shelter. It's a cause that's close to my heart.</t>
-  </si>
-  <si>
-    <t>That's a wonderful idea!</t>
-  </si>
-  <si>
-    <t>That's a great idea!</t>
-  </si>
-  <si>
-    <t>That's a wonderful idea.</t>
-  </si>
-  <si>
-    <t>That's a kind and selfless decision.</t>
+    <t>SFTANNO-000156-0001</t>
+  </si>
+  <si>
+    <t>There are! You can start with small changes, like rearranging furniture or adding plants to boost the energy in your space.</t>
+  </si>
+  <si>
+    <t>Wow, I had no idea! Thanks for the tips!</t>
+  </si>
+  <si>
+    <t>That's a good idea. I never thought about the impact of plants on energy flow.</t>
+  </si>
+  <si>
+    <t>I didn't think about that. Thanks for the tips!</t>
+  </si>
+  <si>
+    <t>That's a great suggestion! I'll definitely have to give that a try.</t>
+  </si>
+  <si>
+    <t>That sounds doable. I never thought about incorporating plants into Feng Shui.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000007-0001</t>
+  </si>
+  <si>
+    <t>They actually offered me the job!</t>
+  </si>
+  <si>
+    <t>Congratulations! That's fantastic news!</t>
+  </si>
+  <si>
+    <t>That's amazing news! Congratulations!</t>
+  </si>
+  <si>
+    <t>That's great news!</t>
+  </si>
+  <si>
+    <t>Congratulations!</t>
   </si>
   <si>
     <t>SFTANNO-000025-0001</t>
@@ -221,151 +235,148 @@
     <t>That's a great idea.</t>
   </si>
   <si>
-    <t>SFTANNO-000054-0001</t>
-  </si>
-  <si>
-    <t>I'm really into rap music, especially conscious hip-hop that tackles social issues.</t>
-  </si>
-  <si>
-    <t>That's interesting, I don't usually listen to rap but I'm open to checking out some conscious hip-hop.</t>
-  </si>
-  <si>
-    <t>That's really interesting, I'm not really into rap, but I appreciate the message behind it.</t>
-  </si>
-  <si>
-    <t>I appreciate when music can bring awareness to important issues.</t>
-  </si>
-  <si>
-    <t>I can see why that would resonate with you.</t>
-  </si>
-  <si>
-    <t>That's really interesting, what artists do you recommend?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000005-0001</t>
-  </si>
-  <si>
-    <t>I'm so happy with my new prescription sunglasses. They make everything so much clearer!</t>
-  </si>
-  <si>
-    <t>That's fantastic! New glasses can really change your life.</t>
-  </si>
-  <si>
-    <t>That's great to hear! I love sunglasses too.</t>
-  </si>
-  <si>
-    <t>That's awesome! I'm glad you're happy with them.</t>
-  </si>
-  <si>
-    <t>That's fantastic! It's great when you find the perfect pair.</t>
-  </si>
-  <si>
-    <t>That's great! I'm happy for you.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000020-0001</t>
-  </si>
-  <si>
-    <t>I worry that exploring black holes could be dangerous for us and for our machines.</t>
-  </si>
-  <si>
-    <t>I understand why you would be concerned, but it's also worth considering the potential for new discoveries.</t>
-  </si>
-  <si>
-    <t>It's definitely a risky venture.</t>
-  </si>
-  <si>
-    <t>It's definitely a concern.</t>
-  </si>
-  <si>
-    <t>I understand the concern, but we have to weigh the risks and benefits of exploration.</t>
-  </si>
-  <si>
-    <t>I agree, the potential risks are immense.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000029-0001</t>
-  </si>
-  <si>
-    <t>I can't stand when fashion magazines promote unrealistic body images.</t>
-  </si>
-  <si>
-    <t>I completely agree. It's so frustrating.</t>
-  </si>
-  <si>
-    <t>It's so frustrating that they perpetuate those harmful ideas.</t>
-  </si>
-  <si>
-    <t>It's frustrating how they contribute to the problem.</t>
-  </si>
-  <si>
-    <t>It's so frustrating how the industry perpetuates unhealthy beauty standards.</t>
-  </si>
-  <si>
-    <t>It's infuriating how they manipulate our perceptions.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000060-0001</t>
-  </si>
-  <si>
-    <t>With so many people relying on social media for their news, it's concerning how easy it is for false information to spread.</t>
-  </si>
-  <si>
-    <t>Yes, it's a scary thought to think about the potential consequences of false information being widely circulated.</t>
-  </si>
-  <si>
-    <t>It's a valid concern. It's crucial to fact-check and verify information before sharing it.</t>
-  </si>
-  <si>
-    <t>Yes, it's important for people to be critical thinkers and fact-check information before sharing it.</t>
-  </si>
-  <si>
-    <t>Yes, it's definitely a challenge to combat the spread of misinformation online.</t>
-  </si>
-  <si>
-    <t>I completely agree. It's important to fact-check and be mindful of where we get our news from.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000046-0001</t>
-  </si>
-  <si>
-    <t>Yes, I tried boiling brussels sprouts, and they came out mushy.</t>
-  </si>
-  <si>
-    <t>Ugh, that's the worst.</t>
-  </si>
-  <si>
-    <t>That's too bad.</t>
-  </si>
-  <si>
-    <t>Ugh, boiling vegetables always makes them lose their texture.</t>
-  </si>
-  <si>
-    <t>Boiling vegetables can be hit or miss.</t>
-  </si>
-  <si>
-    <t>Yuck, I hate mushy brussels sprouts.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000012-0001</t>
-  </si>
-  <si>
-    <t>It's sickening to hear about poachers targeting endangered species for their valuable parts.</t>
-  </si>
-  <si>
-    <t>It's despicable and a tragic loss to our planet. We must all work together to put an end to this.</t>
-  </si>
-  <si>
-    <t>It's absolutely reprehensible. We need to strengthen conservation efforts and enforce stricter penalties against poachers.</t>
-  </si>
-  <si>
-    <t>It's a heartbreaking and disgusting crime that needs to be stopped.</t>
-  </si>
-  <si>
-    <t>It's a disgusting and reprehensible practice that must be stopped.</t>
-  </si>
-  <si>
-    <t>It's a terrible crime that must be stopped at all costs.</t>
+    <t>SFTANNO-000167-0001</t>
+  </si>
+  <si>
+    <t>Do you think we'll see the implementation of AI in our daily lives soon?</t>
+  </si>
+  <si>
+    <t>It's hard to say, but I think we're already seeing it happen in many aspects of our lives.</t>
+  </si>
+  <si>
+    <t>It's already happening in many ways, from smart homes to self-driving cars.</t>
+  </si>
+  <si>
+    <t>It's definitely a possibility, especially with how fast technology is advancing.</t>
+  </si>
+  <si>
+    <t>It's already happening to some extent, but I think it will become more widespread in the coming years.</t>
+  </si>
+  <si>
+    <t>It's possible, and it could make our lives easier in some ways.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000001-0001</t>
+  </si>
+  <si>
+    <t>I finished that book you recommended, and it was amazing!</t>
+  </si>
+  <si>
+    <t>I'm thrilled to hear that!</t>
+  </si>
+  <si>
+    <t>I'm so glad you enjoyed it!</t>
+  </si>
+  <si>
+    <t>That's wonderful news!</t>
+  </si>
+  <si>
+    <t>That's fantastic news!</t>
+  </si>
+  <si>
+    <t>SFTANNO-000004-0001</t>
+  </si>
+  <si>
+    <t>I'm worried about my son's eyesight. He's been complaining about headaches lately.</t>
+  </si>
+  <si>
+    <t>That's understandable. It's important to get it checked.</t>
+  </si>
+  <si>
+    <t>That's understandable. It's important to get it checked out.</t>
+  </si>
+  <si>
+    <t>That's concerning. You should definitely take him to get his eyes checked.</t>
+  </si>
+  <si>
+    <t>That sounds really concerning.</t>
+  </si>
+  <si>
+    <t>I can understand why you're concerned.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000000-0001</t>
+  </si>
+  <si>
+    <t>You won't believe it! They killed off my favorite character, and I'm so mad about it!</t>
+  </si>
+  <si>
+    <t>That's so frustrating when that happens.</t>
+  </si>
+  <si>
+    <t>That's awful! I hate when that happens.</t>
+  </si>
+  <si>
+    <t>I know how you feel. It's so infuriating when that happens.</t>
+  </si>
+  <si>
+    <t>That's heartbreaking! I hate it when that happens.</t>
+  </si>
+  <si>
+    <t>That's so frustrating! I'm sorry you had to experience that.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000190-0001</t>
+  </si>
+  <si>
+    <t>I'm afraid I'm becoming addicted to binge-watching.</t>
+  </si>
+  <si>
+    <t>It's easy to get lost in a good series.</t>
+  </si>
+  <si>
+    <t>Binge-watching can be a slippery slope.</t>
+  </si>
+  <si>
+    <t>It's easy to get sucked into a show, but remember to take breaks.</t>
+  </si>
+  <si>
+    <t>It's easy to get sucked into the binge-watching vortex.</t>
+  </si>
+  <si>
+    <t>It's easy to get caught up in binge-watching. How are you managing your screen time?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000161-0001</t>
+  </si>
+  <si>
+    <t>Honestly, I just can't believe the company would put us through this unnecessary anxiety and tension.</t>
+  </si>
+  <si>
+    <t>It's outrageous. They should have handled the situation with more care and consideration.</t>
+  </si>
+  <si>
+    <t>I know, it's completely unacceptable.</t>
+  </si>
+  <si>
+    <t>It's unacceptable how they handled the situation. They should have been more transparent and considerate of their employees' feelings.</t>
+  </si>
+  <si>
+    <t>I completely agree. It's unacceptable how they're handling this situation.</t>
+  </si>
+  <si>
+    <t>I completely agree. It's unacceptable that they would do this to their employees.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000003-0001</t>
+  </si>
+  <si>
+    <t>I have, but the thought of using someone else's lens disgusts me a little.</t>
+  </si>
+  <si>
+    <t>I can understand that, it's important to have your own equipment.</t>
+  </si>
+  <si>
+    <t>I understand where you're coming from, it can be unhygienic to use someone else's equipment.</t>
+  </si>
+  <si>
+    <t>I can understand why you'd feel that way. It's a big investment.</t>
+  </si>
+  <si>
+    <t>I understand, it's not the cleanest option.</t>
+  </si>
+  <si>
+    <t>I can understand why you'd feel that way. It's a common concern.</t>
   </si>
   <si>
     <t>SFTANNO-000018-0001</t>
@@ -389,46 +400,46 @@
     <t>It is incredible, isn't it?</t>
   </si>
   <si>
-    <t>SFTANNO-000010-0001</t>
-  </si>
-  <si>
-    <t>My pet rabbit passed away recently, and I'm struggling to cope with the loss.</t>
-  </si>
-  <si>
-    <t>I'm so sorry for your loss. Rabbits can be so beloved.</t>
-  </si>
-  <si>
-    <t>I'm so sorry to hear that. Losing a pet is never easy.</t>
-  </si>
-  <si>
-    <t>I'm deeply sorry to hear that. Losing a pet is never easy.</t>
-  </si>
-  <si>
-    <t>I'm so sorry for your loss. Pets become such a big part of our lives.</t>
-  </si>
-  <si>
-    <t>I'm so sorry for your loss. Losing a beloved pet can be incredibly tough.</t>
-  </si>
-  <si>
-    <t>SFTANNO-000081-0001</t>
-  </si>
-  <si>
-    <t>That's a great idea, but it's infuriating that it has to come to this.</t>
-  </si>
-  <si>
-    <t>I share your anger. But we can channel that frustration into action.</t>
-  </si>
-  <si>
-    <t>I share your anger. But it's a start.</t>
-  </si>
-  <si>
-    <t>I know. But we must act now.</t>
-  </si>
-  <si>
-    <t>I share your anger. But we can make a difference together.</t>
-  </si>
-  <si>
-    <t>I completely agree. We should be able to enjoy a clean environment without resorting to cleanups.</t>
+    <t>SFTANNO-000002-0001</t>
+  </si>
+  <si>
+    <t>Not yet, everything is still uncertain due to the pandemic.</t>
+  </si>
+  <si>
+    <t>I understand, it's been tough for the industry.</t>
+  </si>
+  <si>
+    <t>That's understandable. It's been tough for everyone in the industry.</t>
+  </si>
+  <si>
+    <t>I completely understand. It's tough to plan anything with so much uncertainty.</t>
+  </si>
+  <si>
+    <t>That's understandable. The pandemic has affected everyone in different ways.</t>
+  </si>
+  <si>
+    <t>That's too bad, but it's understandable. Safety should always come first.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000172-0001</t>
+  </si>
+  <si>
+    <t>I've tried to explain, but it's disheartening when they don't even want to listen.</t>
+  </si>
+  <si>
+    <t>It's infuriating when people refuse to listen.</t>
+  </si>
+  <si>
+    <t>It's frustrating when people are unwilling to open their minds.</t>
+  </si>
+  <si>
+    <t>It's frustrating when people won't listen to your experiences.</t>
+  </si>
+  <si>
+    <t>It's infuriating when people refuse to consider other perspectives.</t>
+  </si>
+  <si>
+    <t>It's tough when people refuse to be open-minded.</t>
   </si>
   <si>
     <t>SFTANNO-000011-0001</t>
@@ -473,25 +484,31 @@
     <t>It's such a difficult balance.</t>
   </si>
   <si>
-    <t>SFTANNO-000032-0001</t>
-  </si>
-  <si>
-    <t>I just got a new watch that tracks my sleep patterns and heart rate!</t>
-  </si>
-  <si>
-    <t>That sounds amazing! I'm so jealous.</t>
-  </si>
-  <si>
-    <t>That's so cool! What's the name of the brand?</t>
-  </si>
-  <si>
-    <t>That's so cool!</t>
-  </si>
-  <si>
-    <t>That's so cool! Technology is amazing.</t>
-  </si>
-  <si>
-    <t>That's amazing! Technology has come so far.</t>
+    <t>SFTANNO-000176-0001</t>
+  </si>
+  <si>
+    <t>No, just a pot for the pasta and a pan for the sauce.</t>
+  </si>
+  <si>
+    <t>Perfect, I have everything I need.</t>
+  </si>
+  <si>
+    <t>Perfect, sounds easy enough.</t>
+  </si>
+  <si>
+    <t>Sounds easy, let's get started!</t>
+  </si>
+  <si>
+    <t>That's great to hear, I don't have a lot of kitchen equipment.</t>
+  </si>
+  <si>
+    <t>That's all you need! It's a simple and satisfying dish.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It seems the context for the user should metion the topic about ballet. Otherwise, this could be consider an hallucination. </t>
+  </si>
+  <si>
+    <t>Falta contexto</t>
   </si>
 </sst>
 </file>
@@ -547,16 +564,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -861,24 +875,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" style="2" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="27.5703125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="27.5703125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="27.5703125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="18.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="27.5703125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="18.5703125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="27.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="27.5703125" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="10.44140625" style="2" customWidth="1"/>
+    <col min="2" max="3" width="27.88671875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="27.88671875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="27.88671875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.77734375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="27.88671875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9" style="2" customWidth="1"/>
+    <col min="13" max="13" width="27.88671875" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -919,7 +933,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -929,35 +943,38 @@
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>2</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3">
-        <v>3</v>
+      <c r="F2" s="2">
+        <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>5</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>4</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="L2" s="2">
+        <v>3</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -967,35 +984,35 @@
       <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3">
-        <v>5</v>
+      <c r="D3" s="2">
+        <v>3</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3">
-        <v>2</v>
+      <c r="F3" s="2">
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3">
-        <v>3</v>
+      <c r="H3" s="2">
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="3">
-        <v>4</v>
+      <c r="J3" s="2">
+        <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="L3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1005,35 +1022,35 @@
       <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3">
-        <v>2</v>
+      <c r="D4" s="2">
+        <v>4</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="3">
-        <v>5</v>
+      <c r="F4" s="2">
+        <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="3">
-        <v>4</v>
+      <c r="H4" s="2">
+        <v>2</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="L4" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1043,35 +1060,35 @@
       <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="3">
-        <v>3</v>
+      <c r="D5" s="2">
+        <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="3">
-        <v>1</v>
+      <c r="F5" s="2">
+        <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>5</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="2">
         <v>2</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+      <c r="L5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1081,35 +1098,35 @@
       <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3">
-        <v>5</v>
+      <c r="D6" s="2">
+        <v>4</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="3">
-        <v>4</v>
+      <c r="F6" s="2">
+        <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="3">
-        <v>3</v>
+      <c r="H6" s="2">
+        <v>5</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>2</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="L6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1119,35 +1136,35 @@
       <c r="C7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>4</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="3">
-        <v>5</v>
+      <c r="F7" s="2">
+        <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="3">
-        <v>3</v>
+      <c r="H7" s="2">
+        <v>5</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="3">
-        <v>2</v>
+      <c r="J7" s="2">
+        <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1157,35 +1174,35 @@
       <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="3">
-        <v>3</v>
+      <c r="D8" s="2">
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="3">
-        <v>5</v>
+      <c r="F8" s="2">
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="3">
-        <v>2</v>
+      <c r="H8" s="2">
+        <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="L8" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>61</v>
       </c>
@@ -1195,35 +1212,35 @@
       <c r="C9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>4</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="3">
-        <v>3</v>
+      <c r="H9" s="2">
+        <v>2</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="3">
-        <v>2</v>
+      <c r="J9" s="2">
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="L9" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="L9" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>68</v>
       </c>
@@ -1233,35 +1250,35 @@
       <c r="C10" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>4</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F10" s="3">
-        <v>5</v>
+      <c r="F10" s="2">
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="H10" s="3">
-        <v>1</v>
+      <c r="H10" s="2">
+        <v>2</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="J10" s="3">
-        <v>2</v>
+      <c r="J10" s="2">
+        <v>1</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="L10" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="L10" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>75</v>
       </c>
@@ -1271,455 +1288,461 @@
       <c r="C11" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="3">
-        <v>2</v>
+      <c r="D11" s="2">
+        <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="F11" s="3">
-        <v>3</v>
+      <c r="F11" s="2">
+        <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="2">
         <v>4</v>
       </c>
       <c r="I11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J11" s="2">
+        <v>1</v>
+      </c>
+      <c r="K11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="J11" s="3">
-        <v>1</v>
-      </c>
-      <c r="K11" s="2" t="s">
+      <c r="L11" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="L11" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="3">
-        <v>2</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F12" s="3">
-        <v>5</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="3">
-        <v>4</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="J12" s="2">
+        <v>5</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="J12" s="3">
-        <v>1</v>
-      </c>
-      <c r="K12" s="2" t="s">
+      <c r="L12" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L12" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="3">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="3">
-        <v>4</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H13" s="3">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2">
+        <v>4</v>
+      </c>
+      <c r="K13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J13" s="3">
-        <v>3</v>
-      </c>
-      <c r="K13" s="2" t="s">
+      <c r="L13" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="L13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D14" s="3">
-        <v>5</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="F14" s="3">
-        <v>4</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>3</v>
-      </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2">
+        <v>3</v>
+      </c>
+      <c r="K14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="J14" s="3">
-        <v>1</v>
-      </c>
-      <c r="K14" s="2" t="s">
+      <c r="L14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="B15" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D15" s="3">
-        <v>3</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2">
+        <v>5</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F15" s="3">
-        <v>4</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H15" s="3">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2">
+        <v>3</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="3">
-        <v>2</v>
-      </c>
-      <c r="K15" s="2" t="s">
+      <c r="L15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="L15" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D16" s="3">
-        <v>4</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="3">
-        <v>5</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2">
+        <v>5</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H16" s="3">
-        <v>2</v>
-      </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2">
+        <v>4</v>
+      </c>
+      <c r="K16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J16" s="3">
-        <v>3</v>
-      </c>
-      <c r="K16" s="2" t="s">
+      <c r="L16" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="L16" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="B17" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F17" s="3">
-        <v>4</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2">
+        <v>5</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="H17" s="3">
-        <v>3</v>
-      </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2">
+        <v>4</v>
+      </c>
+      <c r="K17" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="J17" s="3">
-        <v>2</v>
-      </c>
-      <c r="K17" s="2" t="s">
+      <c r="L17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="L17" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="B18" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2">
+        <v>5</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D18" s="3">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2">
+        <v>4</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F18" s="3">
-        <v>5</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="H18" s="3">
-        <v>4</v>
-      </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" s="2">
+        <v>2</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="J18" s="3">
-        <v>1</v>
-      </c>
-      <c r="K18" s="2" t="s">
+      <c r="L18" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="L18" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B19" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D19" s="3">
-        <v>4</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F19" s="3">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2">
+        <v>4</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="H19" s="3">
-        <v>5</v>
-      </c>
-      <c r="I19" s="2" t="s">
+      <c r="J19" s="2">
+        <v>5</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="J19" s="3">
-        <v>1</v>
-      </c>
-      <c r="K19" s="2" t="s">
+      <c r="L19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="L19" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="3">
-        <v>5</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2">
+        <v>3</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="3">
-        <v>2</v>
-      </c>
-      <c r="I20" s="2" t="s">
+      <c r="J20" s="2">
+        <v>4</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="J20" s="3">
-        <v>3</v>
-      </c>
-      <c r="K20" s="2" t="s">
+      <c r="L20" s="2">
+        <v>5</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="L20" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="3">
-        <v>5</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F21" s="3">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="3">
-        <v>4</v>
-      </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2">
+        <v>4</v>
+      </c>
+      <c r="K21" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="J21" s="3">
-        <v>2</v>
-      </c>
-      <c r="K21" s="2" t="s">
+      <c r="L21" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="L21" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B22" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2">
+        <v>2</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D22" s="3">
-        <v>4</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2">
+        <v>4</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F22" s="3">
-        <v>5</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2">
+        <v>3</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="H22" s="3">
-        <v>3</v>
-      </c>
-      <c r="I22" s="2" t="s">
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="J22" s="3">
-        <v>2</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1</v>
+      <c r="L22" s="2">
+        <v>5</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{83249C0D-3346-46F4-8182-CD771D25A1C7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{ED945E93-CBC4-4693-A9E1-F603378F9128}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
